--- a/tests/fixtures/master_import/Application_test.xlsx
+++ b/tests/fixtures/master_import/Application_test.xlsx
@@ -1,40 +1,477 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+  <si>
+    <t>简历编号</t>
+  </si>
+  <si>
+    <t>二层部门</t>
+  </si>
+  <si>
+    <t>三层部门</t>
+  </si>
+  <si>
+    <t>候选人</t>
+  </si>
+  <si>
+    <t>电话</t>
+  </si>
+  <si>
+    <t>登记状态</t>
+  </si>
+  <si>
+    <t>简历筛选状态</t>
+  </si>
+  <si>
+    <t>资审状态</t>
+  </si>
+  <si>
+    <t>Offer状态</t>
+  </si>
+  <si>
+    <t>签约状态</t>
+  </si>
+  <si>
+    <t>是否入职</t>
+  </si>
+  <si>
+    <t>RS2026001</t>
+  </si>
+  <si>
+    <t>研发一组</t>
+  </si>
+  <si>
+    <t>存储部</t>
+  </si>
+  <si>
+    <t>主表新人</t>
+  </si>
+  <si>
+    <t>13790001001</t>
+  </si>
+  <si>
+    <t>已登记</t>
+  </si>
+  <si>
+    <t>通过</t>
+  </si>
+  <si>
+    <t>未发放</t>
+  </si>
+  <si>
+    <t>未签约</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>RS2026002</t>
+  </si>
+  <si>
+    <t>计算部</t>
+  </si>
+  <si>
+    <t>测试员</t>
+  </si>
+  <si>
+    <t>13911112222</t>
+  </si>
+  <si>
+    <t>已发放</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,85 +479,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -403,191 +1067,128 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="12.25" customWidth="1"/>
+    <col min="4" max="4" width="11.75" customWidth="1"/>
+    <col min="5" max="5" width="14.25" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>简历编号</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>二层部门</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>三层部门</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>候选人</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>电话</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>登记状态</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>简历筛选状态</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>资审状态</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Offer状态</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>签约状态</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>是否入职</t>
-        </is>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>RS2026001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>研发一组</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>存储部</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>主表新人</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>13790001001</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>已登记</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>未发放</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>RS2026002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>研发一组</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>计算部</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>测试员</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>13911112222</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>已登记</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>已发放</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/tests/fixtures/master_import/Application_test.xlsx
+++ b/tests/fixtures/master_import/Application_test.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:AF31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,2227 +424,4905 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>应聘档案编号</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>候选人</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>电话</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>学历</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>毕业院校</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>专业</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>二层部门</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>三层部门</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>拓源人</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>拓源人部门</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>接口人</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>接口人部门</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>来源渠道</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>拟录取工作地</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>登记状态</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>简历筛选状态</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>资审状态</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>笔试状态</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>技术面状态</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>主管面状态</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>报批状态</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>谈薪状态</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>Offer状态</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>签约状态</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>是否入职</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>当前进展</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>入职风险</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>HR内部编号</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>备注说明</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>投递渠道明细</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>校招批次</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RS2026001</t>
+          <t>SR20260101001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>SR20260101001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>主表新人</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>13790001001</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>硕士</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>测试大学</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>软件工程</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>网络部</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>块存储</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>研发一组</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>内推</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0619主表新人进展</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>HR-9001</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>冒烟测试固定行</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RS2026002</t>
+          <t>SR20260102002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>SR20260102002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>测试员</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>13911112222</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>测试大学</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>计算机</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>软件部</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>研发一组</t>
+          <t>存储部</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>块存储</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>熟人推荐</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0619测试员进展</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>HR-9002</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>测试员样例备注</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RS20260003</t>
+          <t>SR20260110003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>王伟婷</t>
+          <t>SR20260110003</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13846913810</t>
+          <t>王强艳</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>本科</t>
+          <t>13878695681</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>复旦大学</t>
+          <t>博士</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>清华大学</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>软件工程</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>存储部</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>块存储</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>研发一组</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>熟人推荐</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>HR-0003</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>王强艳样例备注</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RS20260004</t>
+          <t>SR20260110004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>吴磊伟</t>
+          <t>SR20260110004</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13813999315</t>
+          <t>张勇芳</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>本科</t>
+          <t>13824862807</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>复旦大学</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>软件工程</t>
+          <t>清华大学</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>通信工程</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>存储部</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>对象存储</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>研发一组</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>内推</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>HR-0004</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>张勇芳样例备注</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RS20260005</t>
+          <t>SR20260110005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>周磊敏</t>
+          <t>SR20260110005</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13870291817</t>
+          <t>杨静强</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>博士</t>
+          <t>13857866880</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>上海交通大学</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>人工智能</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>存储部</t>
+          <t>计算机科学</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>对象存储</t>
+          <t>网络部</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>块存储</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>内推</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>HR-0005</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>杨静强样例备注</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RS20260006</t>
+          <t>SR20260110006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>杨强静</t>
+          <t>SR20260110006</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13830868105</t>
+          <t>黄娜勇</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>13851473104</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>南京大学</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>计算机科学</t>
+          <t>浙江大学</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>存储部</t>
+          <t>电子信息</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>研发一组</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>校园宣讲</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>HR-0006</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>黄娜勇样例备注</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RS20260007</t>
+          <t>SR20260110007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>王强超</t>
+          <t>SR20260110007</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13856164955</t>
+          <t>吴艳洋</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>博士</t>
+          <t>13825629378</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>上海交通大学</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>人工智能</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>存储部</t>
+          <t>数据科学</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>研发一组</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>内推</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>HR-0007</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>吴艳洋样例备注</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RS20260008</t>
+          <t>SR20260110008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周芳琳</t>
+          <t>SR20260110008</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13860806024</t>
+          <t>吴洋艳</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>13879523069</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>上海交通大学</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>人工智能</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>网络部</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>对象存储</t>
+          <t>计算部</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>块存储</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>校园宣讲</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>HR-0008</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>吴洋艳样例备注</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RS20260009</t>
+          <t>SR20260110009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>王伟杰</t>
+          <t>SR20260110009</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13840587988</t>
+          <t>杨洋娜</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>13874708126</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>北京大学</t>
+          <t>本科</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>人工智能</t>
+          <t>清华大学</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>计算部</t>
+          <t>通信工程</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>块存储</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>通用计算</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>熟人推荐</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>HR-0009</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>杨洋娜样例备注</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RS20260010</t>
+          <t>SR20260110010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>杨静洋</t>
+          <t>SR20260110010</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13895320121</t>
+          <t>周艳洋</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>13863948553</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>硕士</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>浙江大学</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>北京大学</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>电子信息</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>网络部</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>对象存储</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>块存储</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>校园宣讲</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>HR-0010</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>周艳洋样例备注</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RS20260011</t>
+          <t>SR20260110011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>陈婷琳</t>
+          <t>SR20260110011</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13896977837</t>
+          <t>吴洋艳</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>本科</t>
+          <t>13875701930</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>浙江大学</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>自动化</t>
+          <t>北京大学</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>计算部</t>
+          <t>电子信息</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>对象存储</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>研发一组</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>熟人推荐</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>HR-0011</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>吴洋艳样例备注</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RS20260012</t>
+          <t>SR20260110012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>黄磊静</t>
+          <t>SR20260110012</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13895899313</t>
+          <t>周伟静</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>博士</t>
+          <t>13852500997</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>复旦大学</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>数据科学</t>
+          <t>清华大学</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>通信工程</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>网络部</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>块存储</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>研发一组</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>线上投递</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>HR-0012</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>周伟静样例备注</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RS20260013</t>
+          <t>SR20260110013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>赵超伟</t>
+          <t>SR20260110013</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13852339391</t>
+          <t>黄芳静</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>13876896901</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>硕士</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>上海交通大学</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>计算机科学</t>
+          <t>清华大学</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>计算部</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>通用计算</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>对象存储</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>熟人推荐</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>HR-0013</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>黄芳静样例备注</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RS20260014</t>
+          <t>SR20260110014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>赵杰洋</t>
+          <t>SR20260110014</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13863100814</t>
+          <t>王伟洋</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>13887932180</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>博士</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>中山大学</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>软件工程</t>
+          <t>清华大学</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>网络部</t>
+          <t>数据科学</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>计算部</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>对象存储</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>校园宣讲</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>HR-0014</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>王伟洋样例备注</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RS20260015</t>
+          <t>SR20260110015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>赵婷艳</t>
+          <t>SR20260110015</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13882340307</t>
+          <t>张艳静</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>13899721481</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>武汉大学</t>
+          <t>博士</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>自动化</t>
+          <t>浙江大学</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>存储部</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>通用计算</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>熟人推荐</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>HR-0015</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>张艳静样例备注</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RS20260016</t>
+          <t>SR20260110016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>赵娜艳</t>
+          <t>SR20260110016</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13876238574</t>
+          <t>周敏洋</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>13888911235</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>清华大学</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>人工智能</t>
+          <t>上海交通大学</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>存储部</t>
+          <t>数据科学</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>对象存储</t>
+          <t>网络部</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>块存储</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>熟人推荐</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>HR-0016</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>周敏洋样例备注</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RS20260017</t>
+          <t>SR20260110017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>李浩杰</t>
+          <t>SR20260110017</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>13866661351</t>
+          <t>李勇静</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>博士</t>
+          <t>13878142594</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>北京大学</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>通信工程</t>
+          <t>复旦大学</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
+          <t>计算部</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>研发一组</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>校园宣讲</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>HR-0017</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>李勇静样例备注</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RS20260018</t>
+          <t>SR20260110018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周静艳</t>
+          <t>SR20260110018</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13811540956</t>
+          <t>杨芳伟</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>13856575946</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>博士</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>北京大学</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>数据科学</t>
+          <t>浙江大学</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>网络部</t>
+          <t>计算机科学</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>通用计算</t>
+          <t>存储部</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>研发一组</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>内推</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>HR-0018</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>杨芳伟样例备注</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RS20260019</t>
+          <t>SR20260110019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>王静磊</t>
+          <t>SR20260110019</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>13831227574</t>
+          <t>黄强芳</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>13876782671</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>硕士</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>清华大学</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>上海交通大学</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>数据科学</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>网络部</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
+          <t>计算部</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>对象存储</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>线上投递</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
         <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>HR-0019</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>黄强芳样例备注</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RS20260020</t>
+          <t>SR20260110020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周琳芳</t>
+          <t>SR20260110020</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13893926371</t>
+          <t>吴强洋</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>13890291676</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>复旦大学</t>
+          <t>本科</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>软件工程</t>
+          <t>清华大学</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>网络部</t>
+          <t>数据科学</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>对象存储</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>块存储</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>线上投递</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>HR-0020</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>吴强洋样例备注</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RS20260021</t>
+          <t>SR20260110021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周浩琳</t>
+          <t>SR20260110021</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>13881182864</t>
+          <t>张艳伟</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>本科</t>
+          <t>13870642368</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>南京大学</t>
+          <t>博士</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>北京大学</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>通信工程</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>存储部</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>块存储</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>对象存储</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>线上投递</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>HR-0021</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>张艳伟样例备注</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RS20260022</t>
+          <t>SR20260110022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>刘琳超</t>
+          <t>SR20260110022</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>13851273847</t>
+          <t>李娜娜</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>本科</t>
+          <t>13862341080</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>清华大学</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>软件工程</t>
+          <t>复旦大学</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>存储部</t>
+          <t>数据科学</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>块存储</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>熟人推荐</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
         <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>HR-0022</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>李娜娜样例备注</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RS20260023</t>
+          <t>SR20260110023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>黄超芳</t>
+          <t>SR20260110023</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>13881498611</t>
+          <t>李强娜</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>本科</t>
+          <t>13845358813</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>浙江大学</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>数据科学</t>
+          <t>复旦大学</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>通信工程</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>对象存储</t>
+          <t>网络部</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>研发一组</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>线上投递</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>HR-0023</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>李强娜样例备注</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RS20260024</t>
+          <t>SR20260110024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>陈艳超</t>
+          <t>SR20260110024</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>13891415657</t>
+          <t>周洋洋</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>13826120303</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>复旦大学</t>
+          <t>博士</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>自动化</t>
+          <t>上海交通大学</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>计算部</t>
+          <t>电子信息</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>通用计算</t>
+          <t>存储部</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>对象存储</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>线上投递</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>HR-0024</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>周洋洋样例备注</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RS20260025</t>
+          <t>SR20260110025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>杨杰杰</t>
+          <t>SR20260110025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>13860119651</t>
+          <t>王洋强</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>13864761163</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>中山大学</t>
+          <t>博士</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>北京大学</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>计算机科学</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>计算部</t>
-        </is>
-      </c>
       <c r="H26" t="inlineStr">
         <is>
+          <t>网络部</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>对象存储</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>内推</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
         <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>HR-0025</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>王洋强样例备注</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RS20260026</t>
+          <t>SR20260110026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>王强伟</t>
+          <t>SR20260110026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>13888961459</t>
+          <t>吴艳敏</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>13824722812</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>博士</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>复旦大学</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>自动化</t>
+          <t>浙江大学</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>数据科学</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>计算部</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>块存储</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>通用计算</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>内推</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>HR-0026</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>吴艳敏样例备注</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RS20260027</t>
+          <t>SR20260110027</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>王婷杰</t>
+          <t>SR20260110027</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>13817901903</t>
+          <t>李芳静</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>本科</t>
+          <t>13822942714</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>北京大学</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>计算机科学</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>网络部</t>
-        </is>
-      </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>块存储</t>
+          <t>存储部</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
+          <t>通用计算</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>线上投递</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>HR-0027</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>李芳静样例备注</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RS20260028</t>
+          <t>SR20260110028</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周敏静</t>
+          <t>SR20260110028</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>13899788677</t>
+          <t>周强静</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>13888934594</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>复旦大学</t>
+          <t>本科</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>自动化</t>
+          <t>浙江大学</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>电子信息</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>计算部</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>研发一组</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
+          <t>通用计算</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>内推</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>HR-0028</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>周强静样例备注</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RS20260029</t>
+          <t>SR20260110029</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>赵浩洋</t>
+          <t>SR20260110029</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>13864634663</t>
+          <t>张磊静</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>13865637040</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>北京大学</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>清华大学</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>计算机科学</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>软件部</t>
-        </is>
-      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>通用计算</t>
+          <t>计算部</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>块存储</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>内推</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>HR-0029</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>张磊静样例备注</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RS20260030</t>
+          <t>SR20260110030</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>杨磊洋</t>
+          <t>SR20260110030</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>13817270733</t>
+          <t>王艳勇</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>博士</t>
+          <t>13857017385</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>北京大学</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>计算机科学</t>
+          <t>复旦大学</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>数据科学</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>通用计算</t>
+          <t>存储部</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
+          <t>研发一组</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>hr01</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hr02</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>软件部</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>内推</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>谈薪中</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>HR-0030</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>王艳勇样例备注</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>官网+宣讲会</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>2026春招</t>
         </is>
       </c>
     </row>

--- a/tests/fixtures/master_import/Application_test.xlsx
+++ b/tests/fixtures/master_import/Application_test.xlsx
@@ -581,12 +581,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SR20260101001</t>
+          <t>SR2026010100001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SR20260101001</t>
+          <t>SR2026010100001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -743,12 +743,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SR20260102002</t>
+          <t>SR2026010200002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SR20260102002</t>
+          <t>SR2026010200002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>熟人推荐</t>
+          <t>内推</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -905,12 +905,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SR20260110003</t>
+          <t>SR2026011000003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SR20260110003</t>
+          <t>SR2026011000003</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1063,12 +1063,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SR20260110004</t>
+          <t>SR2026011000004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SR20260110004</t>
+          <t>SR2026011000004</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1221,12 +1221,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SR20260110005</t>
+          <t>SR2026011000005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SR20260110005</t>
+          <t>SR2026011000005</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1379,12 +1379,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SR20260110006</t>
+          <t>SR2026011000006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SR20260110006</t>
+          <t>SR2026011000006</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1537,12 +1537,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SR20260110007</t>
+          <t>SR2026011000007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SR20260110007</t>
+          <t>SR2026011000007</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1695,12 +1695,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SR20260110008</t>
+          <t>SR2026011000008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SR20260110008</t>
+          <t>SR2026011000008</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1853,12 +1853,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SR20260110009</t>
+          <t>SR2026011000009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SR20260110009</t>
+          <t>SR2026011000009</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2011,12 +2011,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SR20260110010</t>
+          <t>SR2026011000010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SR20260110010</t>
+          <t>SR2026011000010</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2169,12 +2169,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SR20260110011</t>
+          <t>SR2026011000011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SR20260110011</t>
+          <t>SR2026011000011</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2327,12 +2327,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SR20260110012</t>
+          <t>SR2026011000012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SR20260110012</t>
+          <t>SR2026011000012</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2485,12 +2485,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SR20260110013</t>
+          <t>SR2026011000013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SR20260110013</t>
+          <t>SR2026011000013</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2643,12 +2643,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SR20260110014</t>
+          <t>SR2026011000014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SR20260110014</t>
+          <t>SR2026011000014</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2801,12 +2801,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SR20260110015</t>
+          <t>SR2026011000015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SR20260110015</t>
+          <t>SR2026011000015</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2959,12 +2959,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SR20260110016</t>
+          <t>SR2026011000016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SR20260110016</t>
+          <t>SR2026011000016</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3117,12 +3117,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SR20260110017</t>
+          <t>SR2026011000017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SR20260110017</t>
+          <t>SR2026011000017</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3275,12 +3275,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SR20260110018</t>
+          <t>SR2026011000018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SR20260110018</t>
+          <t>SR2026011000018</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3433,12 +3433,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SR20260110019</t>
+          <t>SR2026011000019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SR20260110019</t>
+          <t>SR2026011000019</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3591,12 +3591,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SR20260110020</t>
+          <t>SR2026011000020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SR20260110020</t>
+          <t>SR2026011000020</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3749,12 +3749,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SR20260110021</t>
+          <t>SR2026011000021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SR20260110021</t>
+          <t>SR2026011000021</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3907,12 +3907,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SR20260110022</t>
+          <t>SR2026011000022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SR20260110022</t>
+          <t>SR2026011000022</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4065,12 +4065,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SR20260110023</t>
+          <t>SR2026011000023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SR20260110023</t>
+          <t>SR2026011000023</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4223,12 +4223,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SR20260110024</t>
+          <t>SR2026011000024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SR20260110024</t>
+          <t>SR2026011000024</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4381,12 +4381,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SR20260110025</t>
+          <t>SR2026011000025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SR20260110025</t>
+          <t>SR2026011000025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4539,12 +4539,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SR20260110026</t>
+          <t>SR2026011000026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SR20260110026</t>
+          <t>SR2026011000026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4697,12 +4697,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SR20260110027</t>
+          <t>SR2026011000027</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SR20260110027</t>
+          <t>SR2026011000027</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4855,12 +4855,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SR20260110028</t>
+          <t>SR2026011000028</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SR20260110028</t>
+          <t>SR2026011000028</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5013,12 +5013,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SR20260110029</t>
+          <t>SR2026011000029</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SR20260110029</t>
+          <t>SR2026011000029</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5171,12 +5171,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SR20260110030</t>
+          <t>SR2026011000030</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SR20260110030</t>
+          <t>SR2026011000030</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">

--- a/tests/fixtures/master_import/Application_test.xlsx
+++ b/tests/fixtures/master_import/Application_test.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF31"/>
+  <dimension ref="A1:AI24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,70 +509,85 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>商业秘密签署状态</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>笔试状态</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>技术面状态</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>主管面状态</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>报批状态</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>谈薪状态</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Offer状态</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>签约状态</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>是否入职</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>当前环节</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>当前环节状态</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
         <is>
           <t>当前进展</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>入职风险</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>HR内部编号</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>备注说明</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>投递渠道明细</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>校招批次</t>
         </is>
@@ -646,12 +661,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>内推</t>
+          <t>线上投递</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -671,7 +686,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -686,55 +701,62 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>审批中</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>谈薪中</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>0619主表新人进展</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>HR-9001</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>冒烟测试固定行</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -808,12 +830,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>内推</t>
+          <t>线上投递</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -833,7 +855,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -848,55 +870,62 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
           <t>审批中</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>谈薪中</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>0619测试员进展</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>HR-9002</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>测试员样例备注</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -905,32 +934,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SR2026011000003</t>
+          <t>SR2026020100001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SR2026011000003</t>
+          <t>SR2026020100001</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>王强艳</t>
+          <t>状态01投递</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13878695681</t>
+          <t>13790002001</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>博士</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>清华大学</t>
+          <t>测试大学</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -970,91 +999,66 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>熟人推荐</t>
+          <t>线上投递</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>已登记</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>审批中</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>谈薪中</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>未发放</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+          <t>待投递</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>HR-0003</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>王强艳样例备注</t>
+          <t>状态01投递当前进展</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>HR-ST01</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>状态01投递流程状态测试</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -1063,22 +1067,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SR2026011000004</t>
+          <t>SR2026020200002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SR2026011000004</t>
+          <t>SR2026020200002</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>张勇芳</t>
+          <t>状态02简历筛选</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13824862807</t>
+          <t>13790002002</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1088,17 +1092,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>清华大学</t>
+          <t>测试大学</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>通信工程</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>存储部</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1128,12 +1132,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>内推</t>
+          <t>线上投递</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1143,76 +1147,55 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>审批中</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>谈薪中</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>未发放</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+          <t>待筛选</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>HR-0004</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>张勇芳样例备注</t>
+          <t>状态02简历筛选当前进展</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>HR-ST02</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>状态02简历筛选流程状态测试</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -1221,22 +1204,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SR2026011000005</t>
+          <t>SR2026020300003</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SR2026011000005</t>
+          <t>SR2026020300003</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杨静强</t>
+          <t>状态03资格审查</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13857866880</t>
+          <t>13790002003</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1246,22 +1229,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>上海交通大学</t>
+          <t>测试大学</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>计算机科学</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>网络部</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>块存储</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1286,12 +1269,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>内推</t>
+          <t>熟人推荐</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1306,71 +1289,66 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>待审查</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>审批中</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>谈薪中</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>未发放</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+          <t>待签署</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>资审</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>HR-0005</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>杨静强样例备注</t>
+          <t>状态03资格审查当前进展</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>HR-ST03</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>状态03资格审查流程状态测试</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -1379,37 +1357,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SR2026011000006</t>
+          <t>SR2026020400004</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SR2026011000006</t>
+          <t>SR2026020400004</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>黄娜勇</t>
+          <t>状态04商业秘密签署</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13851473104</t>
+          <t>13790002004</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>本科</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>浙江大学</t>
+          <t>测试大学</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>电子信息</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1449,7 +1427,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1469,66 +1447,57 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>待签署</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>审批中</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>谈薪中</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>未发放</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
+          <t>待预约</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>HR-0006</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>黄娜勇样例备注</t>
+          <t>状态04商业秘密签署当前进展</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>HR-ST04</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>状态04商业秘密签署流程状态测试</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -1537,22 +1506,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SR2026011000007</t>
+          <t>SR2026020500005</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SR2026011000007</t>
+          <t>SR2026020500005</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>吴艳洋</t>
+          <t>状态05笔试</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13825629378</t>
+          <t>13790002005</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1562,12 +1531,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>上海交通大学</t>
+          <t>测试大学</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>数据科学</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1602,12 +1571,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>内推</t>
+          <t>线上投递</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1627,66 +1596,65 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>审批中</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>谈薪中</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>未发放</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+          <t>已预约</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>笔试</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>HR-0007</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>吴艳洋样例备注</t>
+          <t>状态05笔试当前进展</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>HR-ST05</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>状态05笔试流程状态测试</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -1695,32 +1663,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SR2026011000008</t>
+          <t>SR2026020600006</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SR2026011000008</t>
+          <t>SR2026020600006</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>吴洋艳</t>
+          <t>状态06性格测评</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13879523069</t>
+          <t>13790002006</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>本科</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>上海交通大学</t>
+          <t>测试大学</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1730,12 +1698,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>计算部</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>块存储</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1760,7 +1728,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>校园宣讲</t>
+          <t>线上投递</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1785,7 +1753,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1793,58 +1761,57 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>审批中</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>谈薪中</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>未发放</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>性格测评</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>HR-0008</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>吴洋艳样例备注</t>
+          <t>状态06性格测评当前进展</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>HR-ST06</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>状态06性格测评流程状态测试</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -1853,37 +1820,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SR2026011000009</t>
+          <t>SR2026020700007</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SR2026011000009</t>
+          <t>SR2026020700007</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杨洋娜</t>
+          <t>状态07资格面试</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13874708126</t>
+          <t>13790002007</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>本科</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>清华大学</t>
+          <t>测试大学</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>通信工程</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1893,7 +1860,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>通用计算</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1918,12 +1885,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>熟人推荐</t>
+          <t>线上投递</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1943,7 +1910,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1951,58 +1918,57 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>审批中</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>谈薪中</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>未发放</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>资格面试</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>HR-0009</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>杨洋娜样例备注</t>
+          <t>状态07资格面试当前进展</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>HR-ST07</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>状态07资格面试流程状态测试</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -2011,22 +1977,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SR2026011000010</t>
+          <t>SR2026020800008</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SR2026011000010</t>
+          <t>SR2026020800008</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>周艳洋</t>
+          <t>状态08技术面</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13863948553</t>
+          <t>13790002008</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2036,22 +2002,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>北京大学</t>
+          <t>测试大学</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>电子信息</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>网络部</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>块存储</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2076,12 +2042,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>校园宣讲</t>
+          <t>内推</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2101,7 +2067,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -2111,56 +2077,59 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>审批中</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>谈薪中</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>未发放</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
+          <t>已预约</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>技术面</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>HR-0010</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>周艳洋样例备注</t>
+          <t>状态08技术面当前进展</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>HR-ST08</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>状态08技术面流程状态测试</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AI11" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -2169,22 +2138,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SR2026011000011</t>
+          <t>SR2026020900009</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SR2026011000011</t>
+          <t>SR2026020900009</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>吴洋艳</t>
+          <t>状态09主管面</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13875701930</t>
+          <t>13790002009</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2194,12 +2163,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>北京大学</t>
+          <t>测试大学</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>电子信息</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2259,7 +2228,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -2274,51 +2243,58 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>审批中</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>谈薪中</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>未发放</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
+          <t>已预约</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>主管面</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>HR-0011</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>吴洋艳样例备注</t>
+          <t>状态09主管面当前进展</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>HR-ST09</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>状态09主管面流程状态测试</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
+      <c r="AI12" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -2327,22 +2303,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SR2026011000012</t>
+          <t>SR2026021000010</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SR2026011000012</t>
+          <t>SR2026021000010</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>周伟静</t>
+          <t>状态10offer策略</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>13852500997</t>
+          <t>13790002010</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2352,17 +2328,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>清华大学</t>
+          <t>测试大学</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>通信工程</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>网络部</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2392,12 +2368,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>线上投递</t>
+          <t>校园宣讲</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2417,7 +2393,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -2432,51 +2408,70 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
           <t>审批中</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>谈薪中</t>
-        </is>
-      </c>
       <c r="X13" t="inlineStr">
         <is>
+          <t>待谈薪</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>报批</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>HR-0012</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>周伟静样例备注</t>
+          <t>状态10offer策略当前进展</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>HR-ST10</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>状态10offer策略流程状态测试</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr">
+      <c r="AI13" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -2485,27 +2480,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SR2026011000013</t>
+          <t>SR2026011000020</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SR2026011000013</t>
+          <t>SR2026011000020</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>黄芳静</t>
+          <t>王强艳</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>13876896901</t>
+          <t>13878695681</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>博士</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2525,7 +2520,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>对象存储</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2555,7 +2550,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2575,7 +2570,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -2590,51 +2585,58 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
           <t>审批中</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>谈薪中</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr">
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>HR-0013</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>黄芳静样例备注</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>HR-0020</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>王强艳样例备注</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
         <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr">
+      <c r="AI14" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -2643,27 +2645,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SR2026011000014</t>
+          <t>SR2026011000021</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SR2026011000014</t>
+          <t>SR2026011000021</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>王伟洋</t>
+          <t>张勇芳</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>13887932180</t>
+          <t>13824862807</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>博士</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2673,17 +2675,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>数据科学</t>
+          <t>通信工程</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>计算部</t>
+          <t>存储部</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>对象存储</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2708,12 +2710,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>校园宣讲</t>
+          <t>内推</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2733,7 +2735,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2748,51 +2750,58 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
           <t>审批中</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>谈薪中</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr">
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>HR-0014</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>王伟洋样例备注</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>HR-0021</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>张勇芳样例备注</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
         <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr">
+      <c r="AI15" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -2801,47 +2810,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SR2026011000015</t>
+          <t>SR2026011000022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SR2026011000015</t>
+          <t>SR2026011000022</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>张艳静</t>
+          <t>杨静强</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13899721481</t>
+          <t>13857866880</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>博士</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>浙江大学</t>
+          <t>上海交通大学</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>软件工程</t>
+          <t>计算机科学</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>存储部</t>
+          <t>网络部</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>通用计算</t>
+          <t>块存储</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2866,12 +2875,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>熟人推荐</t>
+          <t>内推</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2891,7 +2900,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2906,51 +2915,58 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
           <t>审批中</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>谈薪中</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr">
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>HR-0015</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>张艳静样例备注</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>HR-0022</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>杨静强样例备注</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
         <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF16" t="inlineStr">
+      <c r="AI16" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -2959,22 +2975,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SR2026011000016</t>
+          <t>SR2026011000023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SR2026011000016</t>
+          <t>SR2026011000023</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>周敏洋</t>
+          <t>黄娜勇</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13888911235</t>
+          <t>13851473104</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2984,22 +3000,22 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>上海交通大学</t>
+          <t>浙江大学</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>数据科学</t>
+          <t>电子信息</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>网络部</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>块存储</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -3024,12 +3040,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>熟人推荐</t>
+          <t>校园宣讲</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -3049,7 +3065,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -3064,51 +3080,58 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
           <t>审批中</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>谈薪中</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr">
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>HR-0016</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>周敏洋样例备注</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>HR-0023</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>黄娜勇样例备注</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
         <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr">
+      <c r="AI17" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -3117,22 +3140,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SR2026011000017</t>
+          <t>SR2026011000024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SR2026011000017</t>
+          <t>SR2026011000024</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>李勇静</t>
+          <t>吴艳洋</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>13878142594</t>
+          <t>13825629378</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3142,17 +3165,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>复旦大学</t>
+          <t>上海交通大学</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>软件工程</t>
+          <t>数据科学</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>计算部</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -3182,12 +3205,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>校园宣讲</t>
+          <t>内推</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -3207,7 +3230,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -3222,51 +3245,58 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
           <t>审批中</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>谈薪中</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr">
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>HR-0017</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>李勇静样例备注</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>HR-0024</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>吴艳洋样例备注</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
         <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF18" t="inlineStr">
+      <c r="AI18" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -3275,47 +3305,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SR2026011000018</t>
+          <t>SR2026011000025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SR2026011000018</t>
+          <t>SR2026011000025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杨芳伟</t>
+          <t>吴洋艳</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>13856575946</t>
+          <t>13879523069</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>博士</t>
+          <t>本科</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>浙江大学</t>
+          <t>上海交通大学</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>计算机科学</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>存储部</t>
+          <t>计算部</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>研发一组</t>
+          <t>块存储</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3340,12 +3370,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>内推</t>
+          <t>校园宣讲</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3365,7 +3395,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -3380,51 +3410,58 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
           <t>审批中</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>谈薪中</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr">
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>HR-0018</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>杨芳伟样例备注</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>HR-0025</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>吴洋艳样例备注</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
         <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF19" t="inlineStr">
+      <c r="AI19" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -3433,47 +3470,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SR2026011000019</t>
+          <t>SR2026011000026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SR2026011000019</t>
+          <t>SR2026011000026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>黄强芳</t>
+          <t>杨洋娜</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>13876782671</t>
+          <t>13874708126</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>本科</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>上海交通大学</t>
+          <t>清华大学</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>数据科学</t>
+          <t>通信工程</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>计算部</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>对象存储</t>
+          <t>通用计算</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3498,12 +3535,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>线上投递</t>
+          <t>熟人推荐</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3523,7 +3560,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -3538,51 +3575,58 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
           <t>审批中</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>谈薪中</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr">
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>HR-0019</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>黄强芳样例备注</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>HR-0026</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>杨洋娜样例备注</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
         <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF20" t="inlineStr">
+      <c r="AI20" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -3591,42 +3635,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SR2026011000020</t>
+          <t>SR2026011000027</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SR2026011000020</t>
+          <t>SR2026011000027</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>吴强洋</t>
+          <t>周艳洋</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>13890291676</t>
+          <t>13863948553</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>本科</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>清华大学</t>
+          <t>北京大学</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>数据科学</t>
+          <t>电子信息</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>网络部</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3656,7 +3700,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>线上投递</t>
+          <t>校园宣讲</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -3681,7 +3725,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -3696,51 +3740,58 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
           <t>审批中</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>谈薪中</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr">
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>HR-0020</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>吴强洋样例备注</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>HR-0027</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>周艳洋样例备注</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
         <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF21" t="inlineStr">
+      <c r="AI21" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -3749,27 +3800,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SR2026011000021</t>
+          <t>SR2026011000028</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SR2026011000021</t>
+          <t>SR2026011000028</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>张艳伟</t>
+          <t>吴洋艳</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>13870642368</t>
+          <t>13875701930</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>博士</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3779,17 +3830,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>通信工程</t>
+          <t>电子信息</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>存储部</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>对象存储</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3814,12 +3865,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>线上投递</t>
+          <t>熟人推荐</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3839,7 +3890,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -3854,51 +3905,58 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
           <t>审批中</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>谈薪中</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr">
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>HR-0021</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>张艳伟样例备注</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>HR-0028</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>吴洋艳样例备注</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
         <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF22" t="inlineStr">
+      <c r="AI22" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -3907,22 +3965,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SR2026011000022</t>
+          <t>SR2026011000029</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SR2026011000022</t>
+          <t>SR2026011000029</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>李娜娜</t>
+          <t>周伟静</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13862341080</t>
+          <t>13852500997</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3932,22 +3990,22 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>复旦大学</t>
+          <t>清华大学</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>数据科学</t>
+          <t>通信工程</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>网络部</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>块存储</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3972,12 +4030,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>熟人推荐</t>
+          <t>线上投递</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3997,7 +4055,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -4012,51 +4070,58 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
           <t>审批中</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>谈薪中</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr">
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>HR-0022</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>李娜娜样例备注</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>HR-0029</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>周伟静样例备注</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
         <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF23" t="inlineStr">
+      <c r="AI23" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -4065,22 +4130,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SR2026011000023</t>
+          <t>SR2026011000030</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SR2026011000023</t>
+          <t>SR2026011000030</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>李强娜</t>
+          <t>黄芳静</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13845358813</t>
+          <t>13876896901</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4090,22 +4155,22 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>复旦大学</t>
+          <t>清华大学</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>通信工程</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>网络部</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>研发一组</t>
+          <t>对象存储</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4130,12 +4195,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>线上投递</t>
+          <t>熟人推荐</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -4155,7 +4220,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -4170,1157 +4235,58 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
           <t>审批中</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>谈薪中</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>未发放</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>未签约</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr">
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>HR-0023</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>李强娜样例备注</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>HR-0030</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>黄芳静样例备注</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
         <is>
           <t>官网+宣讲会</t>
         </is>
       </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>2026春招</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>SR2026011000024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>SR2026011000024</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>周洋洋</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>13826120303</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>博士</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>上海交通大学</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>电子信息</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>存储部</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>对象存储</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>hr01</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>软件部</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hr02</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>软件部</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>线上投递</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>已登记</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>审批中</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>谈薪中</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>未发放</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>HR-0024</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>周洋洋样例备注</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>2026春招</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>SR2026011000025</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>SR2026011000025</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>王洋强</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>13864761163</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>博士</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>北京大学</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>计算机科学</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>网络部</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>对象存储</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>hr01</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>软件部</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hr02</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>软件部</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>内推</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>已登记</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>审批中</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>谈薪中</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>未发放</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>HR-0025</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>王洋强样例备注</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>2026春招</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>SR2026011000026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>SR2026011000026</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>吴艳敏</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>13824722812</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>博士</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>浙江大学</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>数据科学</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>计算部</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>通用计算</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>hr01</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>软件部</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hr02</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>软件部</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>内推</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>已登记</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>审批中</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>谈薪中</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>未发放</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>HR-0026</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>吴艳敏样例备注</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>2026春招</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>SR2026011000027</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>SR2026011000027</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>李芳静</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>13822942714</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>硕士</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>北京大学</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>计算机科学</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>存储部</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>通用计算</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>hr01</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>软件部</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hr02</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>软件部</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>线上投递</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>已登记</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>审批中</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>谈薪中</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>未发放</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>HR-0027</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>李芳静样例备注</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>2026春招</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>SR2026011000028</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>SR2026011000028</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>周强静</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>13888934594</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>本科</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>浙江大学</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>电子信息</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>计算部</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>通用计算</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>hr01</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>软件部</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hr02</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>软件部</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>内推</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>已登记</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>审批中</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>谈薪中</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>未发放</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>HR-0028</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>周强静样例备注</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>2026春招</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>SR2026011000029</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>SR2026011000029</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>张磊静</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>13865637040</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>本科</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>清华大学</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>计算机科学</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>计算部</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>块存储</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>hr01</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>软件部</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hr02</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>软件部</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>内推</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>已登记</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>审批中</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>谈薪中</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>未发放</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>HR-0029</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>张磊静样例备注</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>2026春招</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>SR2026011000030</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>SR2026011000030</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>王艳勇</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>13857017385</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>硕士</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>复旦大学</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>数据科学</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>存储部</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>研发一组</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>hr01</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>软件部</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hr02</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>软件部</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>内推</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>已登记</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>审批中</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>谈薪中</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>未发放</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>HR-0030</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>王艳勇样例备注</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
+      <c r="AI24" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>

--- a/tests/fixtures/master_import/Application_test.xlsx
+++ b/tests/fixtures/master_import/Application_test.xlsx
@@ -413,181 +413,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI24"/>
+  <dimension ref="A1:AH24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>简历编号</t>
+          <t>应聘档案编号</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>应聘档案编号</t>
+          <t>候选人</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>候选人</t>
+          <t>电话</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>电话</t>
+          <t>学历</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>学历</t>
+          <t>毕业院校</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>毕业院校</t>
+          <t>专业</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>专业</t>
+          <t>二层部门</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>二层部门</t>
+          <t>三层部门</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>三层部门</t>
+          <t>拓源人</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>拓源人</t>
+          <t>拓源人部门</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>拓源人部门</t>
+          <t>接口人</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>接口人</t>
+          <t>接口人部门</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>接口人部门</t>
+          <t>来源渠道</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>来源渠道</t>
+          <t>拟录取工作地</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>拟录取工作地</t>
+          <t>登记状态</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>登记状态</t>
+          <t>简历筛选状态</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>简历筛选状态</t>
+          <t>资审状态</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>资审状态</t>
+          <t>商业秘密签署状态</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>商业秘密签署状态</t>
+          <t>笔试状态</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>笔试状态</t>
+          <t>技术面状态</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>技术面状态</t>
+          <t>主管面状态</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>主管面状态</t>
+          <t>报批状态</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>报批状态</t>
+          <t>谈薪状态</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>谈薪状态</t>
+          <t>Offer状态</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Offer状态</t>
+          <t>签约状态</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>签约状态</t>
+          <t>是否入职</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>是否入职</t>
+          <t>当前环节</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>当前环节</t>
+          <t>当前环节状态</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>当前环节状态</t>
+          <t>当前进展</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>当前进展</t>
+          <t>入职风险</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>入职风险</t>
+          <t>HR内部编号</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>HR内部编号</t>
+          <t>备注说明</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>备注说明</t>
+          <t>投递渠道明细</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
-        <is>
-          <t>投递渠道明细</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
         <is>
           <t>校招批次</t>
         </is>
@@ -601,77 +596,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SR2026010100001</t>
+          <t>主表新人</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>主表新人</t>
+          <t>13790001001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13790001001</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>测试大学</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>测试大学</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>软件工程</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>研发一组</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>内推</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>线上投递</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>已登记</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>已登记</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -681,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>已签署</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -701,62 +696,57 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>审批中</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>审批中</t>
+          <t>谈薪中</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>谈薪中</t>
+          <t>未发放</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>未发放</t>
+          <t>未签约</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0619主表新人进展</t>
+        </is>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0619主表新人进展</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>HR-9001</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>HR-9001</t>
+          <t>冒烟测试固定行</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>冒烟测试固定行</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -770,77 +760,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SR2026010200002</t>
+          <t>测试员</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>测试员</t>
+          <t>13911112222</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13911112222</t>
+          <t>本科</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>本科</t>
+          <t>测试大学</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>测试大学</t>
+          <t>计算机</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>计算机</t>
+          <t>存储部</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>存储部</t>
+          <t>块存储</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>块存储</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>线上投递</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>线上投递</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>已登记</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>已登记</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -850,12 +840,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>已签署</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -870,62 +860,57 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>审批中</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>审批中</t>
+          <t>谈薪中</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>谈薪中</t>
+          <t>未发放</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>未发放</t>
+          <t>未签约</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0619测试员进展</t>
+        </is>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0619测试员进展</t>
+          <t>高</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>HR-9002</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>HR-9002</t>
+          <t>测试员样例备注</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>测试员样例备注</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -939,79 +924,75 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SR2026020100001</t>
+          <t>状态01投递</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>状态01投递</t>
+          <t>13790002001</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13790002001</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>测试大学</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>测试大学</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>软件工程</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>研发一组</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>熟人推荐</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>线上投递</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
           <t>待投递</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
@@ -1020,45 +1001,44 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>未签约</t>
+        </is>
+      </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>状态01投递当前进展</t>
+        </is>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>状态01投递当前进展</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>HR-ST01</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>HR-ST01</t>
+          <t>状态01投递流程状态测试</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>状态01投递流程状态测试</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -1072,84 +1052,80 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SR2026020200002</t>
+          <t>状态02简历筛选</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>状态02简历筛选</t>
+          <t>13790002002</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13790002002</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>测试大学</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>测试大学</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>软件工程</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>研发一组</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>内推</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>线上投递</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>已登记</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>已登记</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
           <t>待筛选</t>
         </is>
       </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -1157,45 +1133,44 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>未签约</t>
+        </is>
+      </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>状态02简历筛选当前进展</t>
+        </is>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>状态02简历筛选当前进展</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>HR-ST02</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>HR-ST02</t>
+          <t>状态02简历筛选流程状态测试</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>状态02简历筛选流程状态测试</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -1209,146 +1184,141 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SR2026020300003</t>
+          <t>状态03资格审查</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>状态03资格审查</t>
+          <t>13790002003</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13790002003</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>测试大学</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>测试大学</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>软件工程</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>研发一组</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>熟人推荐</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>熟人推荐</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>已登记</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>已登记</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>待审查</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>待审查</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
           <t>待签署</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>未签约</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>未签约</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>资审</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>资审</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>状态03资格审查当前进展</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>状态03资格审查当前进展</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>HR-ST03</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>HR-ST03</t>
+          <t>状态03资格审查流程状态测试</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>状态03资格审查流程状态测试</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -1362,77 +1332,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SR2026020400004</t>
+          <t>状态04商业秘密签署</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>状态04商业秘密签署</t>
+          <t>13790002004</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13790002004</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>测试大学</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>测试大学</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>软件工程</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>研发一组</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>线上投递</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>校园宣讲</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>已登记</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>已登记</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1442,62 +1412,57 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>待签署</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>待签署</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
           <t>待预约</t>
         </is>
       </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>未签约</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>状态04商业秘密签署当前进展</t>
+        </is>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>状态04商业秘密签署当前进展</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>HR-ST04</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>HR-ST04</t>
+          <t>状态04商业秘密签署流程状态测试</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>状态04商业秘密签署流程状态测试</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -1511,77 +1476,77 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SR2026020500005</t>
+          <t>状态05笔试</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>状态05笔试</t>
+          <t>13790002005</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13790002005</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>测试大学</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>测试大学</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>软件工程</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>研发一组</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>线上投递</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>线上投递</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>已登记</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>已登记</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1591,70 +1556,65 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>已签署</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
           <t>已预约</t>
         </is>
       </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>未签约</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>未签约</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>笔试</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>笔试</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>状态05笔试当前进展</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>状态05笔试当前进展</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>HR-ST05</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>HR-ST05</t>
+          <t>状态05笔试流程状态测试</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>状态05笔试流程状态测试</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -1668,77 +1628,77 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SR2026020600006</t>
+          <t>状态06性格测评</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>状态06性格测评</t>
+          <t>13790002006</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13790002006</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>测试大学</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>测试大学</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>软件工程</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>研发一组</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>线上投递</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>线上投递</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>已登记</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>已登记</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1748,70 +1708,65 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>已签署</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>未签约</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>未签约</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>性格测评</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>性格测评</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>状态06性格测评当前进展</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>状态06性格测评当前进展</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>HR-ST06</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>HR-ST06</t>
+          <t>状态06性格测评流程状态测试</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>状态06性格测评流程状态测试</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -1825,77 +1780,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SR2026020700007</t>
+          <t>状态07资格面试</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>状态07资格面试</t>
+          <t>13790002007</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13790002007</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>测试大学</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>测试大学</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>软件工程</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>研发一组</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>线上投递</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>线上投递</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>已登记</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>已登记</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1905,70 +1860,65 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>已签署</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>未签约</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>未签约</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>资格面试</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>资格面试</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>状态07资格面试当前进展</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>状态07资格面试当前进展</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>HR-ST07</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>HR-ST07</t>
+          <t>状态07资格面试流程状态测试</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>状态07资格面试流程状态测试</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -1982,77 +1932,77 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SR2026020800008</t>
+          <t>状态08技术面</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>状态08技术面</t>
+          <t>13790002008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13790002008</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>测试大学</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>测试大学</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>软件工程</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>研发一组</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>校园宣讲</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>内推</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>已登记</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>已登记</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -2062,74 +2012,69 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>已签署</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
           <t>已预约</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>未签约</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>未签约</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>技术面</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>技术面</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>状态08技术面当前进展</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>状态08技术面当前进展</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>HR-ST08</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>HR-ST08</t>
+          <t>状态08技术面流程状态测试</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>状态08技术面流程状态测试</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -2143,77 +2088,77 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SR2026020900009</t>
+          <t>状态09主管面</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>状态09主管面</t>
+          <t>13790002009</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13790002009</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>测试大学</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>测试大学</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>软件工程</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>研发一组</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>线上投递</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>熟人推荐</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>已登记</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>已登记</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -2223,12 +2168,12 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>已签署</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -2238,63 +2183,58 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
           <t>已预约</t>
         </is>
       </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>未签约</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>未签约</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>主管面</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>主管面</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>状态09主管面当前进展</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>状态09主管面当前进展</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>HR-ST09</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>HR-ST09</t>
+          <t>状态09主管面流程状态测试</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>状态09主管面流程状态测试</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -2308,77 +2248,77 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SR2026021000010</t>
+          <t>状态10offer策略</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>状态10offer策略</t>
+          <t>13790002010</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>13790002010</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>测试大学</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>测试大学</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>软件工程</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>研发一组</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>线上投递</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>校园宣讲</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>已登记</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>已登记</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2388,12 +2328,12 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>已签署</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -2408,70 +2348,65 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>审批中</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>审批中</t>
+          <t>待谈薪</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>待谈薪</t>
+          <t>未发放</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>未发放</t>
+          <t>未签约</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>未签约</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>报批</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>报批</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>状态10offer策略当前进展</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>状态10offer策略当前进展</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>HR-ST10</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>HR-ST10</t>
+          <t>状态10offer策略流程状态测试</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>状态10offer策略流程状态测试</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -2485,77 +2420,77 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SR2026011000020</t>
+          <t>王强艳</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>王强艳</t>
+          <t>13878695681</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>13878695681</t>
+          <t>博士</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>博士</t>
+          <t>清华大学</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>清华大学</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>软件工程</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>研发一组</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>熟人推荐</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>熟人推荐</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>已登记</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>已登记</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2565,12 +2500,12 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>已签署</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -2585,58 +2520,53 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>审批中</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>审批中</t>
+          <t>谈薪中</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>谈薪中</t>
+          <t>未发放</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>未发放</t>
+          <t>未签约</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>HR-0020</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>HR-0020</t>
+          <t>王强艳样例备注</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>王强艳样例备注</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -2650,77 +2580,77 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SR2026011000021</t>
+          <t>张勇芳</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>张勇芳</t>
+          <t>13824862807</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>13824862807</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>清华大学</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>清华大学</t>
+          <t>通信工程</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>通信工程</t>
+          <t>存储部</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>存储部</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>研发一组</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>内推</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>内推</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>已登记</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>已登记</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2730,12 +2660,12 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>已签署</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2750,58 +2680,53 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>审批中</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>审批中</t>
+          <t>谈薪中</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>谈薪中</t>
+          <t>未发放</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>未发放</t>
+          <t>未签约</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>HR-0021</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>HR-0021</t>
+          <t>张勇芳样例备注</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>张勇芳样例备注</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -2815,77 +2740,77 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SR2026011000022</t>
+          <t>杨静强</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杨静强</t>
+          <t>13857866880</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13857866880</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>上海交通大学</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>上海交通大学</t>
+          <t>计算机科学</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>计算机科学</t>
+          <t>网络部</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>网络部</t>
+          <t>块存储</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>块存储</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>内推</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>内推</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>已登记</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>已登记</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2895,12 +2820,12 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>已签署</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2915,58 +2840,53 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>审批中</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>审批中</t>
+          <t>谈薪中</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>谈薪中</t>
+          <t>未发放</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>未发放</t>
+          <t>未签约</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>HR-0022</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>HR-0022</t>
+          <t>杨静强样例备注</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>杨静强样例备注</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -2980,77 +2900,77 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SR2026011000023</t>
+          <t>黄娜勇</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>黄娜勇</t>
+          <t>13851473104</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13851473104</t>
+          <t>本科</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>本科</t>
+          <t>浙江大学</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>浙江大学</t>
+          <t>电子信息</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>电子信息</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>研发一组</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>校园宣讲</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>校园宣讲</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>已登记</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>已登记</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -3060,12 +2980,12 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>已签署</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -3080,58 +3000,53 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>审批中</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>审批中</t>
+          <t>谈薪中</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>谈薪中</t>
+          <t>未发放</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>未发放</t>
+          <t>未签约</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>HR-0023</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>HR-0023</t>
+          <t>黄娜勇样例备注</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>黄娜勇样例备注</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -3145,77 +3060,77 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SR2026011000024</t>
+          <t>吴艳洋</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>吴艳洋</t>
+          <t>13825629378</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>13825629378</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>上海交通大学</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>上海交通大学</t>
+          <t>数据科学</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>数据科学</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>研发一组</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>内推</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>内推</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>已登记</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>已登记</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -3225,12 +3140,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>已签署</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -3245,58 +3160,53 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>审批中</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>审批中</t>
+          <t>谈薪中</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>谈薪中</t>
+          <t>未发放</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>未发放</t>
+          <t>未签约</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>HR-0024</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>HR-0024</t>
+          <t>吴艳洋样例备注</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>吴艳洋样例备注</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -3310,77 +3220,77 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SR2026011000025</t>
+          <t>吴洋艳</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>吴洋艳</t>
+          <t>13879523069</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>13879523069</t>
+          <t>本科</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>本科</t>
+          <t>上海交通大学</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>上海交通大学</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>软件工程</t>
+          <t>计算部</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>计算部</t>
+          <t>块存储</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>块存储</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>校园宣讲</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>校园宣讲</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>已登记</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>已登记</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -3390,12 +3300,12 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>已签署</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -3410,58 +3320,53 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>审批中</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>审批中</t>
+          <t>谈薪中</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>谈薪中</t>
+          <t>未发放</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>未发放</t>
+          <t>未签约</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>HR-0025</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>HR-0025</t>
+          <t>吴洋艳样例备注</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>吴洋艳样例备注</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -3475,77 +3380,77 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SR2026011000026</t>
+          <t>杨洋娜</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杨洋娜</t>
+          <t>13874708126</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>13874708126</t>
+          <t>本科</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>本科</t>
+          <t>清华大学</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>清华大学</t>
+          <t>通信工程</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>通信工程</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>通用计算</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>通用计算</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>熟人推荐</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>熟人推荐</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>已登记</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>已登记</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -3555,12 +3460,12 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>已签署</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -3575,58 +3480,53 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>审批中</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>审批中</t>
+          <t>谈薪中</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>谈薪中</t>
+          <t>未发放</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>未发放</t>
+          <t>未签约</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>HR-0026</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>HR-0026</t>
+          <t>杨洋娜样例备注</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>杨洋娜样例备注</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -3640,77 +3540,77 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SR2026011000027</t>
+          <t>周艳洋</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>周艳洋</t>
+          <t>13863948553</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>13863948553</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>北京大学</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>北京大学</t>
+          <t>电子信息</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>电子信息</t>
+          <t>网络部</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>网络部</t>
+          <t>块存储</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>块存储</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>校园宣讲</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>校园宣讲</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>已登记</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>已登记</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3720,12 +3620,12 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>已签署</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -3740,58 +3640,53 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>审批中</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>审批中</t>
+          <t>谈薪中</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>谈薪中</t>
+          <t>未发放</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>未发放</t>
+          <t>未签约</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>HR-0027</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>HR-0027</t>
+          <t>周艳洋样例备注</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>周艳洋样例备注</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -3805,77 +3700,77 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SR2026011000028</t>
+          <t>吴洋艳</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>吴洋艳</t>
+          <t>13875701930</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>13875701930</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>北京大学</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>北京大学</t>
+          <t>电子信息</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>电子信息</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>研发一组</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>熟人推荐</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>熟人推荐</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>已登记</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>已登记</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -3885,12 +3780,12 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>已签署</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -3905,58 +3800,53 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>审批中</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>审批中</t>
+          <t>谈薪中</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>谈薪中</t>
+          <t>未发放</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>未发放</t>
+          <t>未签约</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>HR-0028</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>HR-0028</t>
+          <t>吴洋艳样例备注</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>吴洋艳样例备注</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -3970,77 +3860,77 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SR2026011000029</t>
+          <t>周伟静</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>周伟静</t>
+          <t>13852500997</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13852500997</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>清华大学</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>清华大学</t>
+          <t>通信工程</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>通信工程</t>
+          <t>网络部</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>网络部</t>
+          <t>研发一组</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>研发一组</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>线上投递</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>线上投递</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>已登记</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>已登记</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -4050,12 +3940,12 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>已签署</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -4070,58 +3960,53 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>审批中</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>审批中</t>
+          <t>谈薪中</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>谈薪中</t>
+          <t>未发放</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>未发放</t>
+          <t>未签约</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>HR-0029</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>HR-0029</t>
+          <t>周伟静样例备注</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>周伟静样例备注</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
@@ -4135,77 +4020,77 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SR2026011000030</t>
+          <t>黄芳静</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>黄芳静</t>
+          <t>13876896901</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13876896901</t>
+          <t>硕士</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>硕士</t>
+          <t>清华大学</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>清华大学</t>
+          <t>软件工程</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>软件工程</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>对象存储</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>对象存储</t>
+          <t>hr01</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>hr01</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>hr02</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>hr02</t>
+          <t>软件部</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>软件部</t>
+          <t>熟人推荐</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>熟人推荐</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>已登记</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>已登记</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -4215,12 +4100,12 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>已签署</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>已签署</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -4235,58 +4120,53 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>审批中</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>审批中</t>
+          <t>谈薪中</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>谈薪中</t>
+          <t>未发放</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>未发放</t>
+          <t>未签约</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>未签约</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>HR-0030</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>HR-0030</t>
+          <t>黄芳静样例备注</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>黄芳静样例备注</t>
+          <t>官网+宣讲会</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
-        <is>
-          <t>官网+宣讲会</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
         <is>
           <t>2026春招</t>
         </is>
